--- a/Matriz_de_casos_.xlsx
+++ b/Matriz_de_casos_.xlsx
@@ -1,30 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crish\Downloads\Certificados\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11910"/>
+    <workbookView windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
   <si>
     <t xml:space="preserve"> QA Test: https://www.saucedemo.com/</t>
   </si>
@@ -41,55 +44,47 @@
     <t>Pasos</t>
   </si>
   <si>
+    <t>Data</t>
+  </si>
+  <si>
     <t>Resultado esperado</t>
   </si>
   <si>
     <t>Modulo</t>
   </si>
   <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Autenticación</t>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>001_formulario_login_ingreso_exitoso</t>
+  </si>
+  <si>
+    <t>validar que el usuario pueda ingresar con credenciales validas.</t>
+  </si>
+  <si>
+    <t>1. ingresar a la pagína https://www.saucedemo.com/ 
+2. ingresar el usuario validos.
+3. ingresar el password validos.
+4. clic en boton "Login"</t>
   </si>
   <si>
     <t>username: standard_user
 password:secret_sauce</t>
   </si>
   <si>
-    <t>validar que el usuario pueda ingresar con credenciales validas</t>
-  </si>
-  <si>
     <t>El usuario debe poder ver la pagína de inicio.</t>
   </si>
   <si>
-    <t>caso_formulario_login_ingreso_exitoso</t>
-  </si>
-  <si>
-    <t>caso_formulario_login_ingreso_campo_username_vacio</t>
-  </si>
-  <si>
-    <t>validar que el usuario no pueda ingresar si el campo username es vacio</t>
-  </si>
-  <si>
-    <t>username: 
-password:secret_sauce</t>
-  </si>
-  <si>
-    <t>caso_formulario_login_ingreso_campo_password_vacio</t>
-  </si>
-  <si>
-    <t>validar que el usuario no pueda ingresar si el campo password es vacio</t>
-  </si>
-  <si>
-    <t>username: standard_user
-password:</t>
-  </si>
-  <si>
-    <t>caso_formulario_login_ingreso_usuario_no_registrado</t>
-  </si>
-  <si>
-    <t>validar que el usuario no registrado pueda ingresar al sistema.</t>
+    <t>Autenticación</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>002_formulario_login_ingreso_campo_username_vacio</t>
+  </si>
+  <si>
+    <t>validar que el usuario no pueda ingresar si el campo username es vacio.</t>
   </si>
   <si>
     <t>1. ingresar a la pagína https://www.saucedemo.com/ 
@@ -98,12 +93,38 @@
 4. clic en boton "Login"</t>
   </si>
   <si>
+    <t>username: 
+password:secret_sauce</t>
+  </si>
+  <si>
+    <t>El usuario  debe ver el mensaje "Epic sadface: username is required"</t>
+  </si>
+  <si>
+    <t>003_formulario_login_ingreso_campo_password_vacio</t>
+  </si>
+  <si>
+    <t>validar que el usuario no pueda ingresar si el campo password es vacio.</t>
+  </si>
+  <si>
     <t>1. ingresar a la pagína https://www.saucedemo.com/ 
 2. ingresar el usuario.
 3. No ingresar el password.
 4. clic en boton "Login"</t>
   </si>
   <si>
+    <t>username: standard_user
+password:</t>
+  </si>
+  <si>
+    <t>El usuario debe ver el mensaje "Epic sadface: Password is required"</t>
+  </si>
+  <si>
+    <t>004_formulario_login_ingreso_usuario_no_registrado</t>
+  </si>
+  <si>
+    <t>validar que un usuario no registrado, no pueda ingresar al sistema.</t>
+  </si>
+  <si>
     <t>1. ingresar a la pagína https://www.saucedemo.com/ 
 2. ingresar un usuario no registrado
 3. ingresar el password no valido
@@ -114,13 +135,13 @@
 password: epic</t>
   </si>
   <si>
-    <t>caso_formulario_logout_usuario</t>
-  </si>
-  <si>
-    <t>1. ingresar a la pagína https://www.saucedemo.com/ 
-2. ingresar el usuario validos.
-3. ingresar el password validos.
-4. clic en boton "Login"</t>
+    <t>El usuario  debe ver el mensaje "Epic sadface: Username and password do not match any user in this service"</t>
+  </si>
+  <si>
+    <t>005_formulario_logout_usuario</t>
+  </si>
+  <si>
+    <t>validar que el usuario pueda cerrar sesion en la pagina exitosamente.</t>
   </si>
   <si>
     <t>1. ingresar a la pagína https://www.saucedemo.com/ 
@@ -130,28 +151,141 @@
 5. clic en el boton "LogOut".</t>
   </si>
   <si>
-    <t>El usuario  debe ver el mensaje "Epic sadface: username is required"</t>
-  </si>
-  <si>
-    <t>El usuario debe ver el mensaje "Epic sadface: Password is required"</t>
-  </si>
-  <si>
-    <t>El usuario  debe ver el mensaje "Epic sadface: Username and password do not match any user in this service"</t>
-  </si>
-  <si>
-    <t>validar que el usuario pueda cerrar sesion en la pagina exitosamente.</t>
+    <t>006_ver_detalles_producto</t>
+  </si>
+  <si>
+    <t>validar que el usuario pueda ver los detalles de los productos al seleccionarlos.</t>
+  </si>
+  <si>
+    <t>1. ingresar a la pagína https://www.saucedemo.com/ 
+2. ingresar el usuario validos.
+3. ingresar el password validos.
+4. Seleccionar un producto</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>El usuario  debe ver la pagina de detalles del producto seleccionado.</t>
+  </si>
+  <si>
+    <t>Productos</t>
+  </si>
+  <si>
+    <t>007_agregar_producto_carrito_compras</t>
+  </si>
+  <si>
+    <t>validar que el usuario pueda agregar productos al carrito de compras.</t>
+  </si>
+  <si>
+    <t>1. ingresar a la pagína https://www.saucedemo.com/ 
+2. ingresar el usuario validos.
+3. ingresar el password validos.
+4. Seleccionar un producto.
+5. Clic en el boton "Add to Card"</t>
+  </si>
+  <si>
+    <t>El usuario  debe ver el producto seleccionado en el carrito de compras.</t>
+  </si>
+  <si>
+    <t>008_remove_producto_carrito_compras</t>
+  </si>
+  <si>
+    <t>validar que el usuario pueda eliminar productos del carrito de compras.</t>
+  </si>
+  <si>
+    <t>1. ingresar a la pagína https://www.saucedemo.com/ 
+2. ingresar el usuario validos.
+3. ingresar el password validos.
+4. Seleccionar un producto.
+5. Clic en el boton "Remove"</t>
+  </si>
+  <si>
+    <t>El usuario no debe ver el producto seleccionado en el carrito de compras.</t>
+  </si>
+  <si>
+    <t>009_compra_producto_exitoso_carrito</t>
+  </si>
+  <si>
+    <t>validar que el usuario pueda realizar el pedito de compra.</t>
+  </si>
+  <si>
+    <t>1. ingresar a la pagína https://www.saucedemo.com/ 
+2. ingresar el usuario validos.
+3. ingresar el password validos.
+4. Seleccionar un producto.
+5. Clic en el boton "Checkout"
+6.Ingresar la informacion de compra.
+7. Clic en boton "Finish"</t>
+  </si>
+  <si>
+    <t>010_ordenar_productos_por_orden_alfabetico_descendente</t>
+  </si>
+  <si>
+    <t>validar que el usuario pueda visualizar los productos por orden alfabetico (Z-A)</t>
+  </si>
+  <si>
+    <t>1. ingresar a la pagína https://www.saucedemo.com/ 
+2. ingresar el usuario validos.
+3. ingresar el password validos.
+4. Seleccionar un producto.
+5. En los filtros seleccionar la opcion 'Name Z-A'</t>
+  </si>
+  <si>
+    <t>El usuario debe ver los productos ordenados de la Z-A</t>
+  </si>
+  <si>
+    <t>Filtros</t>
+  </si>
+  <si>
+    <t>011_ordenar_productos_por_orden_alfabetico_ascendente</t>
+  </si>
+  <si>
+    <t>validar que el usuario pueda visualizar los productos por orden alfabetico (A-Z)</t>
+  </si>
+  <si>
+    <t>1. ingresar a la pagína https://www.saucedemo.com/ 
+2. ingresar el usuario validos.
+3. ingresar el password validos.
+4. Seleccionar un producto.
+5. En los filtros seleccionar la opcion 'Name A-Z'</t>
+  </si>
+  <si>
+    <t>El usuario debe ver los productos ordenados de la A-Z</t>
+  </si>
+  <si>
+    <t>011_ordenar_productos_por_precio_mayor_menor</t>
+  </si>
+  <si>
+    <t>validar que el usuario pueda visualizar los productos ordenados por precio de mator a menor</t>
+  </si>
+  <si>
+    <t>1. ingresar a la pagína https://www.saucedemo.com/ 
+2. ingresar el usuario validos.
+3. ingresar el password validos.
+4. Seleccionar un producto.
+5. En los filtros seleccionar la opcion 'Price (low to high)'</t>
+  </si>
+  <si>
+    <t>El usuario debe ver los productos ordenados por precio de mayor a menor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -159,19 +293,162 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -180,12 +457,210 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -195,29 +670,14 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -225,87 +685,400 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Coma" xfId="1" builtinId="3"/>
+    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
+    <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
+    <cellStyle name="Coma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Moneda [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hipervínculo" xfId="6" builtinId="8"/>
+    <cellStyle name="Hipervínculo visitado" xfId="7" builtinId="9"/>
+    <cellStyle name="Nota" xfId="8" builtinId="10"/>
+    <cellStyle name="Texto de advertencia" xfId="9" builtinId="11"/>
+    <cellStyle name="Título" xfId="10" builtinId="15"/>
+    <cellStyle name="Texto explicativo" xfId="11" builtinId="53"/>
+    <cellStyle name="Título 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Título 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Título 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Título 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Entrada" xfId="16" builtinId="20"/>
+    <cellStyle name="Salida" xfId="17" builtinId="21"/>
+    <cellStyle name="Cálculo" xfId="18" builtinId="22"/>
+    <cellStyle name="Celda de comprobación" xfId="19" builtinId="23"/>
+    <cellStyle name="Celda vinculada" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Correcto" xfId="22" builtinId="26"/>
+    <cellStyle name="Incorrecto" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutro" xfId="24" builtinId="28"/>
+    <cellStyle name="Énfasis1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Énfasis1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Énfasis1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Énfasis1" xfId="28" builtinId="32"/>
+    <cellStyle name="Énfasis2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Énfasis2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Énfasis2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Énfasis2" xfId="32" builtinId="36"/>
+    <cellStyle name="Énfasis3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Énfasis3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Énfasis3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Énfasis3" xfId="36" builtinId="40"/>
+    <cellStyle name="Énfasis4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Énfasis4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Énfasis4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Énfasis4" xfId="40" builtinId="44"/>
+    <cellStyle name="Énfasis5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Énfasis5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Énfasis5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Énfasis5" xfId="44" builtinId="48"/>
+    <cellStyle name="Énfasis6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Énfasis6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Énfasis6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Énfasis6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -354,7 +1127,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -389,7 +1162,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -563,215 +1336,394 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:R14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5714285714286" style="1" customWidth="1"/>
     <col min="2" max="2" width="61" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7142857142857" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.1428571428571" style="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7142857142857" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.2857142857143" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5714285714286" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:18">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="H2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+    </row>
+    <row r="3" ht="75" spans="1:18">
+      <c r="A3" s="9">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" ht="75" spans="1:18">
+      <c r="A4" s="9">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" ht="75" spans="1:18">
+      <c r="A5" s="9">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="90" spans="1:18">
+      <c r="A6" s="9">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="90" spans="1:18">
+      <c r="A7" s="9">
         <v>5</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="B7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" ht="75" spans="1:18">
+      <c r="A8" s="9">
         <v>6</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
+      <c r="B8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <v>1</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="10" t="s">
+    <row r="9" ht="90" spans="1:18">
+      <c r="A9" s="9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" ht="90" spans="1:18">
+      <c r="A10" s="9">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" ht="135" spans="1:18">
+      <c r="A11" s="17">
+        <v>9</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" ht="105" spans="1:18">
+      <c r="A12" s="17">
         <v>10</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="12" t="s">
+      <c r="B12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" s="18"/>
+    </row>
+    <row r="13" ht="105" spans="1:18">
+      <c r="A13" s="17">
         <v>11</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>8</v>
-      </c>
+      <c r="B13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="18"/>
     </row>
-    <row r="4" spans="1:18" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <v>2</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <v>3</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="90" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <v>4</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="90" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <v>5</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="F10" s="13"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E11" s="13"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D12" s="13"/>
-      <c r="F12" s="13"/>
+    <row r="14" ht="105" spans="1:18">
+      <c r="A14" s="17">
+        <v>11</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Matriz_de_casos_.xlsx
+++ b/Matriz_de_casos_.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="28800" windowHeight="11580"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Casos de prueba" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="68">
   <si>
     <t xml:space="preserve"> QA Test: https://www.saucedemo.com/</t>
   </si>
@@ -207,7 +207,7 @@
     <t>009_compra_producto_exitoso_carrito</t>
   </si>
   <si>
-    <t>validar que el usuario pueda realizar el pedito de compra.</t>
+    <t>validar que el usuario pueda realizar el pedido de compra.</t>
   </si>
   <si>
     <t>1. ingresar a la pagína https://www.saucedemo.com/ 
@@ -254,10 +254,26 @@
     <t>El usuario debe ver los productos ordenados de la A-Z</t>
   </si>
   <si>
-    <t>011_ordenar_productos_por_precio_mayor_menor</t>
-  </si>
-  <si>
-    <t>validar que el usuario pueda visualizar los productos ordenados por precio de mator a menor</t>
+    <t>012_ordenar_productos_por_precio_mayor_menor</t>
+  </si>
+  <si>
+    <t>validar que el usuario pueda visualizar los productos ordenados por precio de mayor a menor</t>
+  </si>
+  <si>
+    <t>1. ingresar a la pagína https://www.saucedemo.com/ 
+2. ingresar el usuario validos.
+3. ingresar el password validos.
+4. Seleccionar un producto.
+5. En los filtros seleccionar la opcion 'Price (hight o low)'</t>
+  </si>
+  <si>
+    <t>El usuario debe ver los productos ordenados por precio de mayor a menor</t>
+  </si>
+  <si>
+    <t>013_ordenar_productos_por_precio_menor_meyor</t>
+  </si>
+  <si>
+    <t>validar que el usuario pueda visualizar los productos ordenados por precio menor a mayor</t>
   </si>
   <si>
     <t>1. ingresar a la pagína https://www.saucedemo.com/ 
@@ -267,7 +283,7 @@
 5. En los filtros seleccionar la opcion 'Price (low to high)'</t>
   </si>
   <si>
-    <t>El usuario debe ver los productos ordenados por precio de mayor a menor</t>
+    <t>El usuario debe ver los productos ordenados por precio de menor a mayor</t>
   </si>
 </sst>
 </file>
@@ -280,7 +296,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,13 +313,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -448,7 +457,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -469,12 +478,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -602,12 +605,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -821,67 +818,70 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -896,46 +896,49 @@
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -944,10 +947,10 @@
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -956,17 +959,11 @@
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -984,9 +981,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1013,12 +1007,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1342,7 +1330,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.5714285714286" style="1" customWidth="1"/>
@@ -1398,325 +1386,357 @@
       <c r="G2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
     </row>
     <row r="3" ht="75" spans="1:18">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" ht="75" spans="1:18">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" ht="75" spans="1:18">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" ht="90" spans="1:18">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>4</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" ht="90" spans="1:18">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>5</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" ht="75" spans="1:18">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>6</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" ht="90" spans="1:18">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>7</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" ht="90" spans="1:18">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>8</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" ht="135" spans="1:18">
-      <c r="A11" s="17">
+      <c r="A11" s="8">
         <v>9</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" ht="105" spans="1:18">
-      <c r="A12" s="17">
+      <c r="A12" s="8">
         <v>10</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H12" s="18"/>
+      <c r="H12" s="13" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="13" ht="105" spans="1:18">
-      <c r="A13" s="17">
+      <c r="A13" s="8">
         <v>11</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H13" s="18"/>
+      <c r="H13" s="13" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="14" ht="105" spans="1:18">
-      <c r="A14" s="17">
-        <v>11</v>
-      </c>
-      <c r="B14" s="10" t="s">
+      <c r="A14" s="8">
+        <v>12</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H14" s="18"/>
+      <c r="H14" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" ht="105" spans="1:18">
+      <c r="A15" s="8">
+        <v>13</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
